--- a/artfynd/A 28012-2023 artfynd.xlsx
+++ b/artfynd/A 28012-2023 artfynd.xlsx
@@ -675,52 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115413258</v>
+        <v>115417717</v>
       </c>
       <c r="B2" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hidberget, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574479</v>
+        <v>574480</v>
       </c>
       <c r="R2" t="n">
         <v>7205654</v>
@@ -792,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115417717</v>
+        <v>115413258</v>
       </c>
       <c r="B3" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,31 +793,36 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hidberget, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574480</v>
+        <v>574479</v>
       </c>
       <c r="R3" t="n">
         <v>7205654</v>
